--- a/product_upload/packages/11/file.xlsx
+++ b/product_upload/packages/11/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>RESPAL 4 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-D5B24B2BC784</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1030,6 +1040,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>RESPAL 2 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-93C812E416BF</t>
         </is>
       </c>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1220,6 +1235,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>RESOVA 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-E5923955D1F3</t>
         </is>
       </c>
@@ -1243,7 +1263,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1414,6 +1434,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>RESOVA 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-69FE8BC754F9</t>
         </is>
       </c>
@@ -1437,7 +1462,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1600,6 +1625,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>REMINYL 4 MG - ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-1B0D50B37A38</t>
         </is>
       </c>
@@ -1623,7 +1653,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1782,6 +1812,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>RESCLAR 500MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-0FE5EEE45A6A</t>
         </is>
       </c>
@@ -1805,7 +1840,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1968,6 +2003,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>RESOLVE PLUS 1.0 CREAM</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-DA7D711E0643</t>
         </is>
       </c>
@@ -1991,7 +2031,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2154,6 +2194,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>REMEFLIN 8 MG-PEARL</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-5F2C747B7FD7</t>
         </is>
       </c>
@@ -2177,7 +2222,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2348,6 +2393,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>RELESTAT 0.05% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-7DE35BA7EAAE</t>
         </is>
       </c>
@@ -2371,7 +2421,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2530,6 +2580,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>RELENZA 5MG POWDER FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-9D67C9644735</t>
         </is>
       </c>
@@ -2553,7 +2608,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2720,6 +2775,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>RELAXON CAP</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-27BCE02AB96D</t>
         </is>
       </c>
@@ -2743,7 +2803,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2910,6 +2970,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>REGAINE TOPICAL SOLN 2%</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-65BBD6A9CF8A</t>
         </is>
       </c>
@@ -2933,7 +2998,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3096,6 +3161,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>REGAINE 5% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-FEA1A6D7DE86</t>
         </is>
       </c>
@@ -3119,7 +3189,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3286,6 +3356,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>REFRESH TEARS 0.5% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-E4752C8BCF30</t>
         </is>
       </c>
@@ -3309,7 +3384,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3476,6 +3551,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>REFRESH P.M.EYE OINT.</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-5102E0389B9B</t>
         </is>
       </c>
@@ -3499,7 +3579,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3666,6 +3746,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>REFRESH LIQUIGEL 1% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-67D9023D0ABA</t>
         </is>
       </c>
@@ -3689,7 +3774,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3852,6 +3937,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t xml:space="preserve">RECTACURE </t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-231C96AD30DF</t>
         </is>
       </c>
@@ -3875,7 +3965,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4042,6 +4132,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>RIASERTAL 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-0ED0B2C275B1</t>
         </is>
       </c>
@@ -4065,7 +4160,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4232,6 +4327,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>RIAPHYLLIN 60MG/5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-D2C83B51A07D</t>
         </is>
       </c>
@@ -4255,7 +4355,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4426,6 +4526,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>RIAPHAN 15 mg per 5 ml</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-323B691B1E38</t>
         </is>
       </c>
@@ -4449,7 +4554,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4616,6 +4721,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>RIANEST</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-D9590918ADCD</t>
         </is>
       </c>
@@ -4639,7 +4749,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4798,6 +4908,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>RIANEST</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-C9AE5999A43C</t>
         </is>
       </c>
@@ -4821,7 +4936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4988,6 +5103,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>RIANEST</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-1E1F37D29FB8</t>
         </is>
       </c>
@@ -5011,7 +5131,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5178,6 +5298,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>RIALOX</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-439CB6A9E74D</t>
         </is>
       </c>
@@ -5201,7 +5326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5372,6 +5497,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>RIALOCAINE 2 % Gel</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-535F26ADC650</t>
         </is>
       </c>
@@ -5395,7 +5525,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5558,6 +5688,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>RIASERTAL 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-A0F34AB9FCF6</t>
         </is>
       </c>
@@ -5581,7 +5716,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5752,6 +5887,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>RIDON 2 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-FD2090D5ACC8</t>
         </is>
       </c>
@@ -5775,7 +5915,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5942,6 +6082,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>RIDON 1 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-C662DAF2B150</t>
         </is>
       </c>
@@ -5965,7 +6110,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6136,6 +6281,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>RIBAVIN 200 MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-A1702AC5FB73</t>
         </is>
       </c>
@@ -6159,7 +6309,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6322,6 +6472,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>RIAZOLIN</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-299FB2DAB8EB</t>
         </is>
       </c>
@@ -6345,7 +6500,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6504,6 +6659,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>RIAZOLE</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-C6F0F547AA5E</t>
         </is>
       </c>
@@ -6527,7 +6687,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6690,6 +6850,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>RIAXINE</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-4215FA4F4296</t>
         </is>
       </c>
@@ -6713,7 +6878,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6872,6 +7037,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>RIATROPINE 1%</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-016137B4A54C</t>
         </is>
       </c>
@@ -6895,7 +7065,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7058,6 +7228,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>RIATROPINE 0.5%</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-F1561DD1229C</t>
         </is>
       </c>
@@ -7081,7 +7256,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7252,6 +7427,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>RIAGESIC</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-E25A735570AD</t>
         </is>
       </c>
@@ -7275,7 +7455,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7434,6 +7614,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>RHEUFACT 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-1DF92C1A2ED0</t>
         </is>
       </c>
@@ -7457,7 +7642,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7620,6 +7805,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>RHEUFACT 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-057E7ED38E6F</t>
         </is>
       </c>
@@ -7643,7 +7833,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7806,6 +7996,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>RETROVIR CAPS 100MG</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-8E5316AA9B57</t>
         </is>
       </c>
@@ -7829,7 +8024,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7992,6 +8187,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>RETROVIR 50MG\5ML ORAL SUSPENTION</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-D64F06292A70</t>
         </is>
       </c>
@@ -8015,7 +8215,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8178,6 +8378,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>RESTAMINE 5 MG -5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-13FC0F5BB396</t>
         </is>
       </c>
@@ -8201,7 +8406,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8368,6 +8573,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>RHINASE 0.05% AQUEOUS NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-F74F86881DE2</t>
         </is>
       </c>
@@ -8391,7 +8601,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8562,6 +8772,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Rhinathiol Promethazine</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-360AFF7E4F1A</t>
         </is>
       </c>
@@ -8585,7 +8800,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8748,6 +8963,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>RIACHOL EYE OINT.1%</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-D0B77AAE6A53</t>
         </is>
       </c>
@@ -8771,7 +8991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8942,6 +9162,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>RIACHOL 5% EAR DROPS</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-77CEBB00DD84</t>
         </is>
       </c>
@@ -8965,7 +9190,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9132,6 +9357,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>RIACHOL 0.5% EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-D8D2FF7936A6</t>
         </is>
       </c>
@@ -9155,7 +9385,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9314,6 +9544,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>RIACAVILOL 6.25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-009BF3AA3D6E</t>
         </is>
       </c>
@@ -9337,7 +9572,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9500,6 +9735,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>RIACAVILOL 12.5 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-CF89DBAA0EAF</t>
         </is>
       </c>
@@ -9523,7 +9763,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9700,6 +9940,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>RHINOCORT AQUA 64MCG NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-F886EAC56948</t>
         </is>
       </c>
@@ -9723,7 +9968,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9886,6 +10131,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>RHINATHIOL EXPECTORANT CARBOCISTEINE 5% SYRUP FOR ADULT</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-3014B3B54241</t>
         </is>
       </c>
@@ -9909,7 +10159,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10076,6 +10326,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>RHINATHIOL SYRUP 20MG-ML CHILDREN</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-558D08DC4B88</t>
         </is>
       </c>
@@ -10099,7 +10354,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10258,6 +10513,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>RIACAVILOL 25MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-B442605E5B9A</t>
         </is>
       </c>
@@ -10281,7 +10541,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10448,6 +10708,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>SEMBRINA TABLETS 250 MG.</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-6D9FFC155A72</t>
         </is>
       </c>
@@ -10471,7 +10736,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10634,6 +10899,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>SEPTANEST N 1-200000 DENTAL CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-653E3C9483EB</t>
         </is>
       </c>
@@ -10657,7 +10927,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10824,6 +11094,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>SEPTANEST SP 1-100000 DENTAL CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-C175482E6693</t>
         </is>
       </c>
@@ -10847,7 +11122,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11018,6 +11293,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>SORTIVA FORTE 100MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-A7883271CA97</t>
         </is>
       </c>
@@ -11041,7 +11321,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11208,6 +11488,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>SORTIVA 50 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-C3AF1BEBFF09</t>
         </is>
       </c>
@@ -11231,7 +11516,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11390,6 +11675,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>SORTIVA 25 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-F418DB31ECA7</t>
         </is>
       </c>
@@ -11413,7 +11703,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11576,6 +11866,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>SORTIVA H 50-12.5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-D2A4AA13795C</t>
         </is>
       </c>
@@ -11599,7 +11894,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11766,6 +12061,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>SORTIVA H 100-25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-79BE596A0F39</t>
         </is>
       </c>
@@ -11789,7 +12089,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11948,6 +12248,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>SORBITOL IRRIGATION 3.3% IN PLASTIC BAG</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-18B4F3F384FF</t>
         </is>
       </c>
@@ -11971,7 +12276,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12134,6 +12439,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>SORBIT 5 G POWDER PACKET</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-3799FC123596</t>
         </is>
       </c>
@@ -12157,7 +12467,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12324,6 +12634,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>SOLVEX 4MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-1DA3F3346E58</t>
         </is>
       </c>
@@ -12347,7 +12662,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12514,6 +12829,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>SPASMEX 30MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-3BC1990DD403</t>
         </is>
       </c>
@@ -12537,7 +12857,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12704,6 +13024,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>SPASMOPAN 10MG TAB.</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-265A407154FF</t>
         </is>
       </c>
@@ -12727,7 +13052,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12898,6 +13223,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>STALORAL MITES MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-E2194D1BB69A</t>
         </is>
       </c>
@@ -12921,7 +13251,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13084,6 +13414,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>STALORAL MITES INITIAL</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-99D998C1C05B</t>
         </is>
       </c>
@@ -13107,7 +13442,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13270,6 +13605,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>STALORAL ANIMAL ORIGIN INITIAL</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-F9A5DC2172D3</t>
         </is>
       </c>
@@ -13293,7 +13633,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13460,6 +13800,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>STALORAL ANIMAL ORIGIN MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-EA3D6426E6B9</t>
         </is>
       </c>
@@ -13483,7 +13828,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13650,6 +13995,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>STALEVO 50-12.5-200MG FILM COATED TAB.</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-529DCE704EAC</t>
         </is>
       </c>
@@ -13673,7 +14023,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13840,6 +14190,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>STALEVO 200-50-200MG FILM COATED TAB.</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-BE5209309592</t>
         </is>
       </c>
@@ -13863,7 +14218,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14034,6 +14389,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>STALEVO 150-37.5-200MG FILM COATED TAB.</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-189A118BEE7E</t>
         </is>
       </c>
@@ -14057,7 +14417,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14228,6 +14588,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>STALEVO 100-25-200MG FILM COATED TAB.</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-E6F6E52C5B39</t>
         </is>
       </c>
@@ -14251,7 +14616,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14420,6 +14785,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>SPIRIVA 18MCG HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-AD09245E41FD</t>
         </is>
       </c>
@@ -14443,7 +14813,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14602,6 +14972,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>SPEDIFEN 600MG GRANULES</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-324CC0801136</t>
         </is>
       </c>
@@ -14625,7 +15000,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14788,6 +15163,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>SPEDIFEN 400MG GRANULES</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-294A5C845590</t>
         </is>
       </c>
@@ -14811,7 +15191,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14982,6 +15362,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>SPASMOTALIN 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-C9A92D619CE6</t>
         </is>
       </c>
@@ -15005,7 +15390,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15172,6 +15557,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>STALORAL MOULDS INITIAL</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-BF0BCCC01DCA</t>
         </is>
       </c>
@@ -15195,7 +15585,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15374,6 +15764,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE IRRIGATION 0.9%</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-3788D728DF5A</t>
         </is>
       </c>
@@ -15397,7 +15792,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15560,6 +15955,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE IRRIGATION 0.9%</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-89ECC0680640</t>
         </is>
       </c>
@@ -15583,7 +15983,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15754,6 +16154,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE IRRIGATION 0.9%</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-3855AD7E72F8</t>
         </is>
       </c>
@@ -15777,7 +16182,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15936,6 +16341,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>SOLPADEINE SOLUBLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-128076655267</t>
         </is>
       </c>
@@ -15959,7 +16369,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16122,6 +16532,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>SOLOTIK 50MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-3A0365E28810</t>
         </is>
       </c>
@@ -16145,7 +16560,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16312,6 +16727,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>SOLOTIK 50MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-D0C01BD00117</t>
         </is>
       </c>
@@ -16335,7 +16755,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16498,6 +16918,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>SOLOTIK 100MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-718984516456</t>
         </is>
       </c>
@@ -16521,7 +16946,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16680,6 +17105,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>SOLOTIK 100MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-77A4B4357A5F</t>
         </is>
       </c>
@@ -16703,7 +17133,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16858,6 +17288,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>SOJOURN 100% VAPOUR LIQUID FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-9B203DC1CF6E</t>
         </is>
       </c>
@@ -16881,7 +17316,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17044,6 +17479,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE0.225% &amp; GLUCOSE 5% I.V</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-FE31C04EAA13</t>
         </is>
       </c>
@@ -17067,7 +17507,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17238,6 +17678,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>STALORAL MOULDS MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-AB15337403F6</t>
         </is>
       </c>
@@ -17261,7 +17706,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17432,6 +17877,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>STALORAL POLLENS MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-13B9BA2EC8C2</t>
         </is>
       </c>
@@ -17455,7 +17905,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17618,6 +18068,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>STUGERON 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-419BE4EB9562</t>
         </is>
       </c>
@@ -17641,7 +18096,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17798,6 +18253,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>STRESS TAB 600</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-AE560EF610A7</t>
         </is>
       </c>
@@ -17821,7 +18281,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17978,6 +18438,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>STRESS TAB 600</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-D2FEC3269118</t>
         </is>
       </c>
@@ -18001,7 +18466,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18164,6 +18629,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>STREPSILS PAIN RELIEF PLUS LOZENGE</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-C5BA634EF5E9</t>
         </is>
       </c>
@@ -18187,7 +18657,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18342,6 +18812,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>STRAVIS 50MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-4FEE3E904554</t>
         </is>
       </c>
@@ -18365,7 +18840,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18532,6 +19007,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>SUPRAX 100 SUSP</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-63C3D7DF3B18</t>
         </is>
       </c>
@@ -18555,7 +19035,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18726,6 +19206,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>SUPRAX 200 CAPS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-447F1CD47789</t>
         </is>
       </c>
@@ -18749,7 +19234,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18916,6 +19401,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>SUPRAX 400 CAPS</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-94E40E35ED78</t>
         </is>
       </c>
@@ -18939,7 +19429,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19116,6 +19606,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>SYMBICORT TURBUHALER</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-4651EF3F090F</t>
         </is>
       </c>
@@ -19139,7 +19634,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19310,6 +19805,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>SYMBICORT 80 MCG/4.5 MCG TURBOHALER</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-C7446C91A18E</t>
         </is>
       </c>
@@ -19333,7 +19833,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19503,6 +20003,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>SURECURE 0.1% TOPICAL GEL</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-C93E39EC4583</t>
         </is>
@@ -19519,7 +20024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19565,100 +20070,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19690,7 +20200,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19705,92 +20215,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-54990</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>162.32</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>13</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19822,7 +20337,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19837,92 +20352,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-86914</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>31.05</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19954,7 +20474,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19969,92 +20489,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-24854</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>423.93</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>15</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20086,7 +20611,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20101,92 +20626,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-57682</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>79.59</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>16</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20218,7 +20748,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20233,92 +20763,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-86663</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>403.45</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>17</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20350,7 +20885,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20365,92 +20900,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-22995</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>59.97</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>18</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20482,7 +21022,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20497,92 +21037,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-65455</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>441.4</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>19</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20614,7 +21159,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20629,92 +21174,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-93365</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>421.31</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20746,7 +21296,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20761,92 +21311,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-72414</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>256.51</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>21</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20878,7 +21433,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20893,92 +21448,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-41728</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>463.94</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>22</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21010,7 +21570,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21025,92 +21585,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-58679</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>437.72</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>23</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21142,7 +21707,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21157,92 +21722,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-57859</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>345.1</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>24</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21259,7 +21829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21365,6 +21935,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21400,7 +21980,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21465,6 +22045,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-06C2A4CA8226</t>
         </is>
@@ -21501,7 +22091,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21566,6 +22156,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-584BE4EC900D</t>
         </is>
@@ -21602,7 +22202,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21667,6 +22267,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-BE29181FC52C</t>
         </is>
@@ -21703,7 +22313,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21768,6 +22378,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-280DD342C793</t>
         </is>
@@ -21804,7 +22424,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21869,6 +22489,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-C581F6BA002C</t>
         </is>
@@ -21905,7 +22535,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21970,6 +22600,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-7F6BB959F962</t>
         </is>
@@ -22006,7 +22646,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22071,6 +22711,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-BEC659B640D0</t>
         </is>
@@ -22107,7 +22757,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22172,6 +22822,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-8C5CB42F4DD7</t>
         </is>
@@ -22208,7 +22868,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22273,6 +22933,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-57B694679CD8</t>
         </is>
@@ -22309,7 +22979,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22374,6 +23044,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-660A7914870C</t>
         </is>
@@ -22410,7 +23090,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22475,6 +23155,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-80B6AF28938A</t>
         </is>
@@ -22511,7 +23201,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22576,6 +23266,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-25D2D90D3C4E</t>
         </is>
@@ -22612,7 +23312,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22677,6 +23377,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-7BDAD88E9F0D</t>
         </is>
@@ -22713,7 +23423,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22778,6 +23488,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-31E39C0A90E1</t>
         </is>
@@ -22814,7 +23534,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22879,6 +23599,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-C5B7376A18D3</t>
         </is>
@@ -22915,7 +23645,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22980,6 +23710,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-1842A6F4EF10</t>
         </is>
@@ -23016,7 +23756,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23081,6 +23821,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-2ECE1A99BC40</t>
         </is>
@@ -23117,7 +23867,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23182,6 +23932,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-6FBFBB0BCF82</t>
         </is>
@@ -23218,7 +23978,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23283,6 +24043,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-A2F16EFB750A</t>
         </is>
@@ -23319,7 +24089,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23384,6 +24154,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-9F43F795C008</t>
         </is>

--- a/product_upload/packages/11/file.xlsx
+++ b/product_upload/packages/11/file.xlsx
@@ -1470,8 +1470,16 @@
           <t>7317502374-718-457562243946</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REMINYL 4 MG - ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>REMINYL 4 MG - ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1661,8 +1669,16 @@
           <t>9687421114-803-849855359760</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESCLAR 500MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RESCLAR 500MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1848,8 +1864,16 @@
           <t>7196990541-677-620553686730</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESOLVE PLUS 1.0 CREAM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RESOLVE PLUS 1.0 CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2039,8 +2063,16 @@
           <t>7543436777-023-228030231849</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REMEFLIN 8 MG-PEARL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>REMEFLIN 8 MG-PEARL detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2429,8 +2461,16 @@
           <t>5303801047-969-351203016845</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RELENZA 5MG POWDER FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>RELENZA 5MG POWDER FOR INHALATION detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2811,8 +2851,16 @@
           <t>5961141955-888-229742710456</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REGAINE TOPICAL SOLN 2%</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>REGAINE TOPICAL SOLN 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3006,8 +3054,16 @@
           <t>7937869874-182-487056489890</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REGAINE 5% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>REGAINE 5% TOPICAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3782,8 +3838,16 @@
           <t>8402537155-999-356524971576</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RECTACURE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>RECTACURE detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4757,8 +4821,16 @@
           <t>4667304373-405-223767487517</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIANEST</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>RIANEST detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5139,8 +5211,16 @@
           <t>0782954606-660-615457465829</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIALOX</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RIALOX detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -6508,8 +6588,16 @@
           <t>0841962335-862-427607717010</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIAZOLE</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>RIAZOLE detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6886,8 +6974,16 @@
           <t>1044797500-286-884332557489</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIATROPINE 1%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>RIATROPINE 1% detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7463,8 +7559,16 @@
           <t>0125583221-634-914132306826</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RHEUFACT 20MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>RHEUFACT 20MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7650,8 +7754,16 @@
           <t>9741893841-250-817896970721</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RHEUFACT 10MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>RHEUFACT 10MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7841,8 +7953,16 @@
           <t>8345126831-553-549548008400</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RETROVIR CAPS 100MG</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>RETROVIR CAPS 100MG detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8032,8 +8152,16 @@
           <t>1494717558-826-514896349900</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RETROVIR 50MG\5ML ORAL SUSPENTION</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>RETROVIR 50MG\5ML ORAL SUSPENTION detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8223,8 +8351,16 @@
           <t>4268234456-839-378825495326</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESTAMINE 5 MG -5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>RESTAMINE 5 MG -5 ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -9393,8 +9529,16 @@
           <t>2782697411-227-996056240771</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIACAVILOL 6.25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>RIACAVILOL 6.25 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9580,8 +9724,16 @@
           <t>0986388223-991-399894433959</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIACAVILOL 12.5 MG TAB</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>RIACAVILOL 12.5 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -10362,8 +10514,16 @@
           <t>2041498478-936-012443813353</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIACAVILOL 25MG TABLET</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>RIACAVILOL 25MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10549,8 +10709,16 @@
           <t>1491487391-985-278509057151</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEMBRINA TABLETS 250 MG.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SEMBRINA TABLETS 250 MG. detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10744,8 +10912,16 @@
           <t>9293404188-668-945398357938</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEPTANEST N 1-200000 DENTAL CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SEPTANEST N 1-200000 DENTAL CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10935,8 +11111,16 @@
           <t>6059219527-640-957522880837</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEPTANEST SP 1-100000 DENTAL CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SEPTANEST SP 1-100000 DENTAL CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11524,8 +11708,16 @@
           <t>5129230593-441-932121533524</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SORTIVA 25 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SORTIVA 25 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -12097,8 +12289,16 @@
           <t>8904992501-070-085326633018</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SORBITOL IRRIGATION 3.3% IN PLASTIC BAG</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SORBITOL IRRIGATION 3.3% IN PLASTIC BAG detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12284,8 +12484,16 @@
           <t>2340427901-649-624295131816</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SORBIT 5 G POWDER PACKET</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SORBIT 5 G POWDER PACKET detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -14821,8 +15029,16 @@
           <t>5824634783-540-607595164398</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPEDIFEN 600MG GRANULES</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>SPEDIFEN 600MG GRANULES detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15008,8 +15224,16 @@
           <t>1991876847-475-757169784377</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPEDIFEN 400MG GRANULES</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SPEDIFEN 400MG GRANULES detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15800,8 +16024,16 @@
           <t>8426239478-593-954352530780</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE IRRIGATION 0.9%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE IRRIGATION 0.9% detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15991,8 +16223,16 @@
           <t>3512013988-343-968647092720</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE IRRIGATION 0.9%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE IRRIGATION 0.9% detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16190,8 +16430,16 @@
           <t>6726012634-052-217424473697</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOLPADEINE SOLUBLE TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>SOLPADEINE SOLUBLE TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16954,8 +17202,16 @@
           <t>2286325847-904-497840501579</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOLOTIK 100MG F-C TABLETS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>SOLOTIK 100MG F-C TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17141,8 +17397,16 @@
           <t>8145032371-080-975512631786</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOJOURN 100% VAPOUR LIQUID FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SOJOURN 100% VAPOUR LIQUID FOR INHALATION detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17324,8 +17588,16 @@
           <t>5925454377-830-653481472465</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE0.225% &amp; GLUCOSE 5% I.V</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE0.225% &amp; GLUCOSE 5% I.V detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -18104,8 +18376,16 @@
           <t>4832475364-760-321928686555</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRESS TAB 600</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>STRESS TAB 600 detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18289,8 +18569,16 @@
           <t>4531416507-078-779470339362</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRESS TAB 600</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>STRESS TAB 600 detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18474,8 +18762,16 @@
           <t>3305055437-530-861767490862</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STREPSILS PAIN RELIEF PLUS LOZENGE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>STREPSILS PAIN RELIEF PLUS LOZENGE detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18665,8 +18961,16 @@
           <t>5616425233-207-087765078667</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRAVIS 50MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>STRAVIS 50MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/11/file.xlsx
+++ b/product_upload/packages/11/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22133,7 +22133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22214,40 +22214,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22327,38 +22332,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>458.9</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-06C2A4CA8226</t>
         </is>
@@ -22438,38 +22448,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>140.91</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-584BE4EC900D</t>
         </is>
@@ -22549,38 +22564,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>446.94</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-BE29181FC52C</t>
         </is>
@@ -22660,38 +22680,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>341.7</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-280DD342C793</t>
         </is>
@@ -22771,38 +22796,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>143.82</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-C581F6BA002C</t>
         </is>
@@ -22882,38 +22912,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>102.67</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-7F6BB959F962</t>
         </is>
@@ -22993,38 +23028,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>337.34</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-BEC659B640D0</t>
         </is>
@@ -23104,38 +23144,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>195.62</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-8C5CB42F4DD7</t>
         </is>
@@ -23215,38 +23260,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>468.21</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-57B694679CD8</t>
         </is>
@@ -23326,38 +23376,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>375.13</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-660A7914870C</t>
         </is>
@@ -23437,38 +23492,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>422.16</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-80B6AF28938A</t>
         </is>
@@ -23548,38 +23608,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>168.09</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-25D2D90D3C4E</t>
         </is>
@@ -23659,38 +23724,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>83.64</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-7BDAD88E9F0D</t>
         </is>
@@ -23770,38 +23840,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>178.43</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-31E39C0A90E1</t>
         </is>
@@ -23881,38 +23956,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>64.65000000000001</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-C5B7376A18D3</t>
         </is>
@@ -23992,38 +24072,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>418.52</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-1842A6F4EF10</t>
         </is>
@@ -24103,38 +24188,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>127.22</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-2ECE1A99BC40</t>
         </is>
@@ -24214,38 +24304,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>195.17</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-6FBFBB0BCF82</t>
         </is>
@@ -24325,38 +24420,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>99.95999999999999</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-A2F16EFB750A</t>
         </is>
@@ -24436,38 +24536,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>342.78</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-9F43F795C008</t>
         </is>
